--- a/harmonized_tables_advp/from_37002253_table3_v1.xlsx
+++ b/harmonized_tables_advp/from_37002253_table3_v1.xlsx
@@ -685,7 +685,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -704,19 +704,19 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
@@ -799,7 +799,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -818,19 +818,19 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
@@ -913,7 +913,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -932,19 +932,19 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1046,19 +1046,19 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
@@ -1141,7 +1141,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1160,19 +1160,19 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
@@ -1255,7 +1255,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1274,19 +1274,19 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1388,19 +1388,19 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -1483,7 +1483,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -1502,19 +1502,19 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1597,7 +1597,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -1616,19 +1616,19 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1711,7 +1711,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1730,19 +1730,19 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1844,19 +1844,19 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1958,19 +1958,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -2053,7 +2053,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -2072,19 +2072,19 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -2186,19 +2186,19 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -2281,7 +2281,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -2300,19 +2300,19 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -2395,7 +2395,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -2414,19 +2414,19 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -2509,7 +2509,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -2528,19 +2528,19 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -2623,7 +2623,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -2642,19 +2642,19 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -2737,7 +2737,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -2756,19 +2756,19 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
@@ -2851,7 +2851,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -2870,19 +2870,19 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
@@ -2965,7 +2965,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -2984,19 +2984,19 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
@@ -3079,7 +3079,7 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -3098,19 +3098,19 @@
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -3193,7 +3193,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -3212,19 +3212,19 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
@@ -3307,7 +3307,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -3326,19 +3326,19 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
@@ -3421,7 +3421,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -3440,19 +3440,19 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W26" t="inlineStr"/>
@@ -3535,7 +3535,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -3554,19 +3554,19 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
@@ -3649,7 +3649,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -3668,19 +3668,19 @@
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W28" t="inlineStr"/>
@@ -3763,7 +3763,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -3782,19 +3782,19 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
@@ -3877,7 +3877,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -3896,19 +3896,19 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
@@ -3991,7 +3991,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -4010,19 +4010,19 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
@@ -4105,7 +4105,7 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -4124,19 +4124,19 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
@@ -4219,7 +4219,7 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -4238,19 +4238,19 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -4333,7 +4333,7 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -4352,19 +4352,19 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -4447,7 +4447,7 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -4466,19 +4466,19 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -4561,7 +4561,7 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -4580,19 +4580,19 @@
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
@@ -4675,7 +4675,7 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -4694,19 +4694,19 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
@@ -4789,7 +4789,7 @@
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -4808,19 +4808,19 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W38" t="inlineStr"/>
@@ -4903,7 +4903,7 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -4922,19 +4922,19 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
@@ -5017,7 +5017,7 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -5036,19 +5036,19 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>discovery + Meta-analysis + replication + meta-analysis</t>
+          <t>Meta-analysis + meta-analysis + discovery + replication</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -5150,19 +5150,19 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1000G + UK10K + HRC + minimac4 + TOPMed</t>
+          <t>TOPMed + HRC + UK10K + minimac4 + 1000G</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>EUR + European ancestry + african american + EAS + AA + hispanic + middle-east</t>
+          <t>European ancestry + hispanic + middle-east + EUR + AA + EAS + african american</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>AD + UA + ADC12 + NIALOAD + Genada</t>
+          <t>NIALOAD + Genada + ADC12 + AD + UA</t>
         </is>
       </c>
       <c r="W41" t="inlineStr"/>
